--- a/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20232.xlsx
+++ b/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="46">
   <si>
     <t>Mat</t>
   </si>
@@ -76,25 +76,25 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>DECTOR</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
+    <t>DE ROMAN</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
   </si>
   <si>
     <t>VALENTE</t>
   </si>
   <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>ELIZALDE</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
@@ -103,70 +103,49 @@
     <t>QUESADA</t>
   </si>
   <si>
-    <t>RAYMUNDO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
     <t>SANTOS</t>
   </si>
   <si>
-    <t>VELAZQUEZ</t>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>PULIDO</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
   </si>
   <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>SOTO</t>
-  </si>
-  <si>
-    <t>GALINDO</t>
-  </si>
-  <si>
-    <t>PULIDO</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>OLGUIN</t>
   </si>
   <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>KEVIN ALEXIS</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
-  </si>
-  <si>
-    <t>BRANDON</t>
+    <t>NATHALI</t>
+  </si>
+  <si>
+    <t>MIRIAM AIMAR</t>
+  </si>
+  <si>
+    <t>GUILLERMO ALEXANDER</t>
+  </si>
+  <si>
+    <t>NOEMI DEL ROCIO</t>
   </si>
   <si>
     <t>JUAN EMANUEL</t>
   </si>
   <si>
-    <t>MARISOL</t>
-  </si>
-  <si>
-    <t>JOSE CARMELO</t>
-  </si>
-  <si>
-    <t>ABDIEL ARMANDO</t>
-  </si>
-  <si>
-    <t>AARON</t>
+    <t>BRENDA JANELY</t>
+  </si>
+  <si>
+    <t>GUILLERMO SAUL</t>
   </si>
   <si>
     <t>GAMALIEL</t>
@@ -175,16 +154,7 @@
     <t>JARED DE JESUS</t>
   </si>
   <si>
-    <t>ESTEPHANY</t>
-  </si>
-  <si>
-    <t>MIRIAM AIMAR</t>
-  </si>
-  <si>
     <t>AZUL MARIAM</t>
-  </si>
-  <si>
-    <t>GUILLERMO ALEXANDER</t>
   </si>
 </sst>
 </file>
@@ -728,16 +698,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>54.84</v>
+      </c>
+      <c r="H2">
+        <v>6.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -751,16 +724,19 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>76.19</v>
+      </c>
+      <c r="H3">
+        <v>6.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -774,16 +750,19 @@
         <v>25</v>
       </c>
       <c r="D4">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>96</v>
+      </c>
+      <c r="H4">
+        <v>7.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -797,16 +776,19 @@
         <v>30</v>
       </c>
       <c r="D5">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>80</v>
+      </c>
+      <c r="H5">
+        <v>6.7</v>
       </c>
     </row>
   </sheetData>
@@ -862,16 +844,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G2">
-        <v>58.06</v>
+        <v>54.84</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -888,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G3">
-        <v>61.9</v>
+        <v>76.19</v>
       </c>
       <c r="H3">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -914,16 +896,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G4">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -940,16 +922,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G5">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="H5">
-        <v>6.7</v>
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -959,7 +941,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -991,16 +973,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920236</v>
+        <v>22330051920235</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1014,22 +996,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920396</v>
+        <v>22330051920370</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1037,22 +1019,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920395</v>
+        <v>22330051920314</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1060,16 +1042,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920401</v>
+        <v>22330051920253</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1083,22 +1065,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920288</v>
+        <v>22330051920401</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -1106,22 +1088,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920298</v>
+        <v>22330051920259</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -1129,22 +1111,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920302</v>
+        <v>22330051920402</v>
       </c>
       <c r="B8" t="s">
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -1152,16 +1134,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920304</v>
+        <v>22330051920305</v>
       </c>
       <c r="B9" t="s">
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1175,16 +1157,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920305</v>
+        <v>22330051920312</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D10" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1198,16 +1180,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920312</v>
+        <v>22330051920397</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1216,98 +1198,6 @@
         <v>12</v>
       </c>
       <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920364</v>
-      </c>
-      <c r="B12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920370</v>
-      </c>
-      <c r="B13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" t="s">
-        <v>26</v>
-      </c>
-      <c r="D13" t="s">
-        <v>53</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920397</v>
-      </c>
-      <c r="B14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" t="s">
-        <v>54</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920314</v>
-      </c>
-      <c r="B15" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" t="s">
-        <v>41</v>
-      </c>
-      <c r="D15" t="s">
-        <v>55</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20232.xlsx
+++ b/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="27">
   <si>
     <t>Mat</t>
   </si>
@@ -76,7 +76,7 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>DE ROMAN</t>
+    <t>HERNANDEZ</t>
   </si>
   <si>
     <t>RODRIGUEZ</t>
@@ -85,76 +85,19 @@
     <t>VELAZQUEZ</t>
   </si>
   <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>VALENTE</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>QUESADA</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>CORTES</t>
+    <t>JOSE</t>
   </si>
   <si>
     <t>PAZ</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>PULIDO</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>OLGUIN</t>
-  </si>
-  <si>
-    <t>NATHALI</t>
-  </si>
-  <si>
-    <t>MIRIAM AIMAR</t>
+    <t>JONATAN GILBERTO</t>
+  </si>
+  <si>
+    <t>HECTOR MISAEL</t>
   </si>
   <si>
     <t>GUILLERMO ALEXANDER</t>
-  </si>
-  <si>
-    <t>NOEMI DEL ROCIO</t>
-  </si>
-  <si>
-    <t>JUAN EMANUEL</t>
-  </si>
-  <si>
-    <t>BRENDA JANELY</t>
-  </si>
-  <si>
-    <t>GUILLERMO SAUL</t>
-  </si>
-  <si>
-    <t>GAMALIEL</t>
-  </si>
-  <si>
-    <t>JARED DE JESUS</t>
-  </si>
-  <si>
-    <t>AZUL MARIAM</t>
   </si>
 </sst>
 </file>
@@ -844,16 +787,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>54.84</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="H2">
-        <v>6.6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -870,16 +813,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G3">
-        <v>76.19</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -905,7 +848,7 @@
         <v>96</v>
       </c>
       <c r="H4">
-        <v>8.300000000000001</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -922,16 +865,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G5">
-        <v>80</v>
+        <v>93.33</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -941,7 +884,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -973,22 +916,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920235</v>
+        <v>22330051920405</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -996,22 +939,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920370</v>
+        <v>22330051920279</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1025,10 +968,10 @@
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1037,167 +980,6 @@
         <v>12</v>
       </c>
       <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>22330051920253</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920401</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920259</v>
-      </c>
-      <c r="B7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920402</v>
-      </c>
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920305</v>
-      </c>
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920312</v>
-      </c>
-      <c r="B10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" t="s">
-        <v>44</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920397</v>
-      </c>
-      <c r="B11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" t="s">
-        <v>45</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20232.xlsx
+++ b/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="30">
   <si>
     <t>Mat</t>
   </si>
@@ -76,6 +76,9 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>LLANOS</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
@@ -85,10 +88,16 @@
     <t>VELAZQUEZ</t>
   </si>
   <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
     <t>JOSE</t>
   </si>
   <si>
     <t>PAZ</t>
+  </si>
+  <si>
+    <t>SERGIO</t>
   </si>
   <si>
     <t>JONATAN GILBERTO</t>
@@ -884,7 +893,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -916,22 +925,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920405</v>
+        <v>21330051420317</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -939,16 +948,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920279</v>
+        <v>22330051920405</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -962,24 +971,47 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920314</v>
+        <v>22330051920279</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>22330051920314</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
         <v>12</v>
       </c>
-      <c r="G4">
+      <c r="G5">
         <v>1</v>
       </c>
     </row>
